--- a/templates/CF2_Template_ExistingDraft.xlsx
+++ b/templates/CF2_Template_ExistingDraft.xlsx
@@ -1,64 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection lockStructure="1" workbookAlgorithmName="SHA-512" workbookHashValue="NyzUZmyJcBlqrKMF9zVLu3ig5pbohhQRBcZTlnP4vkHSElVb6X+OcEl3UPMU+fVPoLLDKXpg5VStCUPJn9w86Q==" workbookSaltValue="09mbXxWE4uMRCt1jx3au1w==" workbookSpinCount="100000"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nephro\Desktop\ROMEL\VS Code\beacon_automation\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3011AB9A-8DF6-424A-86DD-5DD9B868857C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="NyzUZmyJcBlqrKMF9zVLu3ig5pbohhQRBcZTlnP4vkHSElVb6X+OcEl3UPMU+fVPoLLDKXpg5VStCUPJn9w86Q==" workbookSaltValue="09mbXxWE4uMRCt1jx3au1w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>TRANSMITTAL NO.</t>
+  </si>
+  <si>
+    <t>NAME OF PATIENT</t>
+  </si>
+  <si>
+    <t>ATTENDING/ NEPHROLOGIST</t>
+  </si>
+  <si>
+    <t>ACCREDITATION NO.</t>
+  </si>
+  <si>
+    <t>TREATMENT DATES</t>
+  </si>
+  <si>
+    <t>TIME (OPTIONAL)</t>
+  </si>
+  <si>
+    <t>PX CONTACT# (OPTIONAL)</t>
+  </si>
+  <si>
+    <t>NOTES: ENTER THE EXISTING TRANSMITTAL NUMBER FOR EACH PATIENT (THE DRAFT MUST ALREADY EXIST IN BEACON — THIS TEMPLATE DOES NOT CREATE A NEW ONE).</t>
+  </si>
+  <si>
+    <t>260803510002</t>
+  </si>
+  <si>
+    <t>MICAYAS, ROLEX S</t>
+  </si>
+  <si>
+    <t>LILIBETH B. IBARRIENTOS</t>
+  </si>
+  <si>
+    <t>1202-0400315-0</t>
+  </si>
+  <si>
+    <t>JULY 1, 2, 3, 4</t>
+  </si>
+  <si>
+    <t>05:25PM-09:25PM</t>
+  </si>
+  <si>
+    <t>JOSEPH FRANCIS B. ASTORGA</t>
+  </si>
+  <si>
+    <t>A/R STAFF</t>
+  </si>
+  <si>
+    <t>09352408339</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -76,124 +131,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -493,139 +481,245 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet1">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="21.28515625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr defaultColWidth="26.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="33.5703125" customWidth="1" style="9" min="1" max="1"/>
-    <col width="38" customWidth="1" style="12" min="2" max="2"/>
-    <col width="36.140625" customWidth="1" style="12" min="3" max="3"/>
-    <col width="37" customWidth="1" style="12" min="4" max="4"/>
-    <col width="36.7109375" customWidth="1" style="13" min="5" max="5"/>
-    <col width="24" customWidth="1" style="12" min="6" max="16384"/>
-    <col width="21.28515625" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="26.33203125" style="6"/>
+    <col min="2" max="4" width="26.33203125" style="1"/>
+    <col min="5" max="5" width="26.33203125" style="2"/>
+    <col min="6" max="6" width="26.33203125" style="1"/>
+    <col min="9" max="16384" width="26.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.25" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>TRANSMITTAL NO.</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>NAME OF PATIENT</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>ATTENDING/ NEPHROLOGIST</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>ACCREDITATION NO.</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>TREATMENT DATES</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
-        <is>
-          <t>TIME (OPTIONAL)</t>
-        </is>
-      </c>
-      <c r="G1" s="15" t="inlineStr">
-        <is>
-          <t>NOTES: ENTER THE EXISTING TRANSMITTAL NUMBER FOR EACH PATIENT (THE DRAFT MUST ALREADY EXIST IN BEACON — THIS TEMPLATE DOES NOT CREATE A NEW ONE).</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="12">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>260803510002</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>MICAYAS, ROLEX S</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>LILIBETH B. IBARRIENTOS</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>1202-0400315-0</t>
-        </is>
-      </c>
-      <c r="E2" s="13" t="inlineStr">
-        <is>
-          <t>JULY 1, 2, 3, 4</t>
-        </is>
-      </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>05:25PM-09:25PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="F3" s="15" t="n"/>
+    <row r="1" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F3" s="9"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G14" s="10"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G19" s="10"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G20" s="10"/>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G23" s="10"/>
+    </row>
+    <row r="24" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G27" s="10"/>
+    </row>
+    <row r="28" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G28" s="10"/>
+    </row>
+    <row r="29" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G29" s="10"/>
+    </row>
+    <row r="30" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G32" s="10"/>
+    </row>
+    <row r="33" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G33" s="10"/>
+    </row>
+    <row r="34" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G34" s="10"/>
+    </row>
+    <row r="35" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G35" s="10"/>
+    </row>
+    <row r="36" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G36" s="10"/>
+    </row>
+    <row r="37" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G37" s="10"/>
+    </row>
+    <row r="38" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G38" s="10"/>
+    </row>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G39" s="10"/>
+    </row>
+    <row r="40" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G40" s="10"/>
+    </row>
+    <row r="41" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G41" s="10"/>
+    </row>
+    <row r="42" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G42" s="10"/>
+    </row>
+    <row r="43" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G43" s="10"/>
+    </row>
+    <row r="44" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G44" s="10"/>
+    </row>
+    <row r="45" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G45" s="10"/>
+    </row>
+    <row r="46" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G46" s="10"/>
+    </row>
+    <row r="47" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G47" s="10"/>
+    </row>
+    <row r="48" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G48" s="10"/>
+    </row>
+    <row r="49" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G49" s="10"/>
+    </row>
+    <row r="50" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G50" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="31.28515625" customWidth="1" style="3" min="1" max="1"/>
-    <col width="11.5703125" customWidth="1" style="3" min="2" max="2"/>
-    <col width="9.140625" customWidth="1" style="3" min="3" max="4"/>
-    <col width="13" customWidth="1" style="3" min="5" max="5"/>
-    <col width="9.140625" customWidth="1" style="3" min="6" max="16384"/>
+    <col min="1" max="1" width="31.33203125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="13" customWidth="1"/>
+    <col min="3" max="4" width="9.109375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="13" style="13" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="13" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>JOSEPH FRANCIS B. ASTORGA</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>A/R STAFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>09352408339</t>
-        </is>
+    <row r="1" spans="1:2" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
